--- a/fig_11_2/data_RF.xlsx
+++ b/fig_11_2/data_RF.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,169 +417,169 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Locus</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sentence_length</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>fraction_sentence_relative</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>relative_clause_length</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>alius</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>antequam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>atque_consonant</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>conjunction</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cum_clause</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>demonstrative</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>dum</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>gerundive</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>idem</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>interrogative</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ipse</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>iste</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>o_interjection</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>preposition</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>priusquam</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>quidam</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>quin</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>quominus</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>reflexive</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>superlative</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ut</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Speaker</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Addressee</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Human/Divine</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Male/Female</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -809,7 +797,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -918,7 +906,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1136,7 +1124,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1243,7 +1231,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1352,7 +1340,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>11</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1461,7 +1449,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>12</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1568,7 +1556,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>13</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1677,7 +1665,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1784,7 +1772,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>16</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1893,7 +1881,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>18</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2000,7 +1988,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>19</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2107,7 +2095,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2216,7 +2204,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>21</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2325,7 +2313,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>23</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2434,7 +2422,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>24</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2541,7 +2529,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>25</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2650,7 +2638,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>27</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2757,7 +2745,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>28</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2866,7 +2854,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>29</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2975,7 +2963,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>30</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3084,7 +3072,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>31</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3193,7 +3181,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>33</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3302,7 +3290,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>36</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3411,7 +3399,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>39</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -3520,7 +3508,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>40</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -3629,7 +3617,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>41</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -3738,7 +3726,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>42</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>44</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -3956,7 +3944,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>47</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -4065,7 +4053,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>48</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -4174,7 +4162,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>49</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -4283,7 +4271,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>50</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -4392,7 +4380,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>53</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -4501,7 +4489,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>54</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -4610,7 +4598,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>55</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -4717,7 +4705,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>57</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -4826,7 +4814,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>58</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -4935,7 +4923,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>59</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -5042,7 +5030,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>64</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -5151,7 +5139,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>65</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -5258,7 +5246,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>66</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -5365,7 +5353,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>67</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -5474,7 +5462,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>69</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -5583,7 +5571,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>70</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -5692,7 +5680,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>71</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -5801,7 +5789,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>72</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -5910,7 +5898,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>74</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -6019,7 +6007,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>75</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -6128,7 +6116,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>77</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -6235,7 +6223,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>78</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -6344,7 +6332,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>81</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -6453,7 +6441,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>83</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -6562,7 +6550,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>85</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -6671,7 +6659,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>86</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -6780,7 +6768,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>87</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -6889,7 +6877,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>88</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -6998,7 +6986,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>89</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -7107,7 +7095,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>90</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -7214,7 +7202,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>91</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -7321,7 +7309,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>92</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -7430,7 +7418,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>93</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -7539,7 +7527,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>94</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -7648,7 +7636,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>95</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -7755,7 +7743,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>98</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -7864,7 +7852,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>100</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -7973,7 +7961,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>101</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -8080,7 +8068,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>102</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -8189,7 +8177,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>103</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -8298,7 +8286,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>104</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -8405,7 +8393,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>105</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -8514,7 +8502,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>106</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -8623,7 +8611,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>107</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -8732,7 +8720,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>108</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -8839,7 +8827,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>112</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -8948,7 +8936,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>113</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -9055,7 +9043,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>115</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -9164,7 +9152,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>116</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -9273,7 +9261,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>117</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -9382,7 +9370,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>118</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -9491,7 +9479,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>120</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -9600,7 +9588,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>122</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -9709,7 +9697,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>124</v>
       </c>
       <c r="B86" t="inlineStr">
